--- a/excel/Deplacement_S2.xlsx
+++ b/excel/Deplacement_S2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="56">
   <si>
     <t>Acteur Dépense</t>
   </si>
@@ -150,6 +150,36 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>02/09/2026</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>KJHK</t>
+  </si>
+  <si>
+    <t>09/08/2026</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>7890987654323456</t>
+  </si>
+  <si>
+    <t>78</t>
   </si>
 </sst>
 </file>
@@ -222,9 +252,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
@@ -257,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.98046875"/>
@@ -627,6 +753,998 @@
         <v>45</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="10">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s" s="10">
+        <v>47</v>
+      </c>
+      <c r="D9" t="n" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E9" t="n" s="10">
+        <v>156.0</v>
+      </c>
+      <c r="F9" t="n" s="10">
+        <v>520.0</v>
+      </c>
+      <c r="G9" t="n" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n" s="10">
+        <v>520.0</v>
+      </c>
+      <c r="I9" t="s" s="11">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s" s="10">
+        <v>49</v>
+      </c>
+      <c r="K9" t="s" s="10">
+        <v>50</v>
+      </c>
+      <c r="L9" t="s" s="10">
+        <v>51</v>
+      </c>
+      <c r="M9" t="s" s="10">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s" s="10">
+        <v>39</v>
+      </c>
+      <c r="O9" t="s" s="11">
+        <v>52</v>
+      </c>
+      <c r="P9" t="s" s="11">
+        <v>53</v>
+      </c>
+      <c r="Q9" t="s" s="11">
+        <v>54</v>
+      </c>
+      <c r="R9" t="s" s="11">
+        <v>55</v>
+      </c>
+      <c r="S9" t="s" s="10">
+        <v>44</v>
+      </c>
+      <c r="T9" t="s" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s" s="12">
+        <v>47</v>
+      </c>
+      <c r="D10" t="n" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E10" t="n" s="12">
+        <v>156.0</v>
+      </c>
+      <c r="F10" t="n" s="12">
+        <v>520.0</v>
+      </c>
+      <c r="G10" t="n" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H10" t="n" s="12">
+        <v>520.0</v>
+      </c>
+      <c r="I10" t="s" s="13">
+        <v>48</v>
+      </c>
+      <c r="J10" t="s" s="12">
+        <v>49</v>
+      </c>
+      <c r="K10" t="s" s="12">
+        <v>50</v>
+      </c>
+      <c r="L10" t="s" s="12">
+        <v>51</v>
+      </c>
+      <c r="M10" t="s" s="12">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s" s="12">
+        <v>39</v>
+      </c>
+      <c r="O10" t="s" s="13">
+        <v>52</v>
+      </c>
+      <c r="P10" t="s" s="13">
+        <v>53</v>
+      </c>
+      <c r="Q10" t="s" s="13">
+        <v>54</v>
+      </c>
+      <c r="R10" t="s" s="13">
+        <v>55</v>
+      </c>
+      <c r="S10" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="T10" t="s" s="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="14">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s" s="14">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="14">
+        <v>47</v>
+      </c>
+      <c r="D11" t="n" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="E11" t="n" s="14">
+        <v>156.0</v>
+      </c>
+      <c r="F11" t="n" s="14">
+        <v>520.0</v>
+      </c>
+      <c r="G11" t="n" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="H11" t="n" s="14">
+        <v>520.0</v>
+      </c>
+      <c r="I11" t="s" s="15">
+        <v>48</v>
+      </c>
+      <c r="J11" t="s" s="14">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s" s="14">
+        <v>50</v>
+      </c>
+      <c r="L11" t="s" s="14">
+        <v>51</v>
+      </c>
+      <c r="M11" t="s" s="14">
+        <v>38</v>
+      </c>
+      <c r="N11" t="s" s="14">
+        <v>39</v>
+      </c>
+      <c r="O11" t="s" s="15">
+        <v>52</v>
+      </c>
+      <c r="P11" t="s" s="15">
+        <v>53</v>
+      </c>
+      <c r="Q11" t="s" s="15">
+        <v>54</v>
+      </c>
+      <c r="R11" t="s" s="15">
+        <v>55</v>
+      </c>
+      <c r="S11" t="s" s="14">
+        <v>44</v>
+      </c>
+      <c r="T11" t="s" s="14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="16">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s" s="16">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s" s="16">
+        <v>47</v>
+      </c>
+      <c r="D12" t="n" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E12" t="n" s="16">
+        <v>156.0</v>
+      </c>
+      <c r="F12" t="n" s="16">
+        <v>520.0</v>
+      </c>
+      <c r="G12" t="n" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="H12" t="n" s="16">
+        <v>520.0</v>
+      </c>
+      <c r="I12" t="s" s="17">
+        <v>48</v>
+      </c>
+      <c r="J12" t="s" s="16">
+        <v>49</v>
+      </c>
+      <c r="K12" t="s" s="16">
+        <v>50</v>
+      </c>
+      <c r="L12" t="s" s="16">
+        <v>51</v>
+      </c>
+      <c r="M12" t="s" s="16">
+        <v>38</v>
+      </c>
+      <c r="N12" t="s" s="16">
+        <v>39</v>
+      </c>
+      <c r="O12" t="s" s="17">
+        <v>52</v>
+      </c>
+      <c r="P12" t="s" s="17">
+        <v>53</v>
+      </c>
+      <c r="Q12" t="s" s="17">
+        <v>54</v>
+      </c>
+      <c r="R12" t="s" s="17">
+        <v>55</v>
+      </c>
+      <c r="S12" t="s" s="16">
+        <v>44</v>
+      </c>
+      <c r="T12" t="s" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="18">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s" s="18">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s" s="18">
+        <v>47</v>
+      </c>
+      <c r="D13" t="n" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="E13" t="n" s="18">
+        <v>156.0</v>
+      </c>
+      <c r="F13" t="n" s="18">
+        <v>520.0</v>
+      </c>
+      <c r="G13" t="n" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="H13" t="n" s="18">
+        <v>520.0</v>
+      </c>
+      <c r="I13" t="s" s="19">
+        <v>48</v>
+      </c>
+      <c r="J13" t="s" s="18">
+        <v>49</v>
+      </c>
+      <c r="K13" t="s" s="18">
+        <v>50</v>
+      </c>
+      <c r="L13" t="s" s="18">
+        <v>51</v>
+      </c>
+      <c r="M13" t="s" s="18">
+        <v>38</v>
+      </c>
+      <c r="N13" t="s" s="18">
+        <v>39</v>
+      </c>
+      <c r="O13" t="s" s="19">
+        <v>52</v>
+      </c>
+      <c r="P13" t="s" s="19">
+        <v>53</v>
+      </c>
+      <c r="Q13" t="s" s="19">
+        <v>54</v>
+      </c>
+      <c r="R13" t="s" s="19">
+        <v>55</v>
+      </c>
+      <c r="S13" t="s" s="18">
+        <v>44</v>
+      </c>
+      <c r="T13" t="s" s="18">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="20">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s" s="20">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s" s="20">
+        <v>47</v>
+      </c>
+      <c r="D14" t="n" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E14" t="n" s="20">
+        <v>156.0</v>
+      </c>
+      <c r="F14" t="n" s="20">
+        <v>520.0</v>
+      </c>
+      <c r="G14" t="n" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H14" t="n" s="20">
+        <v>520.0</v>
+      </c>
+      <c r="I14" t="s" s="21">
+        <v>48</v>
+      </c>
+      <c r="J14" t="s" s="20">
+        <v>49</v>
+      </c>
+      <c r="K14" t="s" s="20">
+        <v>50</v>
+      </c>
+      <c r="L14" t="s" s="20">
+        <v>51</v>
+      </c>
+      <c r="M14" t="s" s="20">
+        <v>38</v>
+      </c>
+      <c r="N14" t="s" s="20">
+        <v>39</v>
+      </c>
+      <c r="O14" t="s" s="21">
+        <v>52</v>
+      </c>
+      <c r="P14" t="s" s="21">
+        <v>53</v>
+      </c>
+      <c r="Q14" t="s" s="21">
+        <v>54</v>
+      </c>
+      <c r="R14" t="s" s="21">
+        <v>55</v>
+      </c>
+      <c r="S14" t="s" s="20">
+        <v>44</v>
+      </c>
+      <c r="T14" t="s" s="20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="22">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="22">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s" s="22">
+        <v>47</v>
+      </c>
+      <c r="D15" t="n" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="E15" t="n" s="22">
+        <v>156.0</v>
+      </c>
+      <c r="F15" t="n" s="22">
+        <v>520.0</v>
+      </c>
+      <c r="G15" t="n" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H15" t="n" s="22">
+        <v>520.0</v>
+      </c>
+      <c r="I15" t="s" s="23">
+        <v>48</v>
+      </c>
+      <c r="J15" t="s" s="22">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s" s="22">
+        <v>50</v>
+      </c>
+      <c r="L15" t="s" s="22">
+        <v>51</v>
+      </c>
+      <c r="M15" t="s" s="22">
+        <v>38</v>
+      </c>
+      <c r="N15" t="s" s="22">
+        <v>39</v>
+      </c>
+      <c r="O15" t="s" s="23">
+        <v>52</v>
+      </c>
+      <c r="P15" t="s" s="23">
+        <v>53</v>
+      </c>
+      <c r="Q15" t="s" s="23">
+        <v>54</v>
+      </c>
+      <c r="R15" t="s" s="23">
+        <v>55</v>
+      </c>
+      <c r="S15" t="s" s="22">
+        <v>44</v>
+      </c>
+      <c r="T15" t="s" s="22">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="24">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s" s="24">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s" s="24">
+        <v>47</v>
+      </c>
+      <c r="D16" t="n" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="E16" t="n" s="24">
+        <v>156.0</v>
+      </c>
+      <c r="F16" t="n" s="24">
+        <v>520.0</v>
+      </c>
+      <c r="G16" t="n" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="H16" t="n" s="24">
+        <v>520.0</v>
+      </c>
+      <c r="I16" t="s" s="25">
+        <v>48</v>
+      </c>
+      <c r="J16" t="s" s="24">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s" s="24">
+        <v>50</v>
+      </c>
+      <c r="L16" t="s" s="24">
+        <v>51</v>
+      </c>
+      <c r="M16" t="s" s="24">
+        <v>38</v>
+      </c>
+      <c r="N16" t="s" s="24">
+        <v>39</v>
+      </c>
+      <c r="O16" t="s" s="25">
+        <v>52</v>
+      </c>
+      <c r="P16" t="s" s="25">
+        <v>53</v>
+      </c>
+      <c r="Q16" t="s" s="25">
+        <v>54</v>
+      </c>
+      <c r="R16" t="s" s="25">
+        <v>55</v>
+      </c>
+      <c r="S16" t="s" s="24">
+        <v>44</v>
+      </c>
+      <c r="T16" t="s" s="24">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="26">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s" s="26">
+        <v>47</v>
+      </c>
+      <c r="D17" t="n" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="E17" t="n" s="26">
+        <v>156.0</v>
+      </c>
+      <c r="F17" t="n" s="26">
+        <v>520.0</v>
+      </c>
+      <c r="G17" t="n" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="H17" t="n" s="26">
+        <v>520.0</v>
+      </c>
+      <c r="I17" t="s" s="27">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s" s="26">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s" s="26">
+        <v>50</v>
+      </c>
+      <c r="L17" t="s" s="26">
+        <v>51</v>
+      </c>
+      <c r="M17" t="s" s="26">
+        <v>38</v>
+      </c>
+      <c r="N17" t="s" s="26">
+        <v>39</v>
+      </c>
+      <c r="O17" t="s" s="27">
+        <v>52</v>
+      </c>
+      <c r="P17" t="s" s="27">
+        <v>53</v>
+      </c>
+      <c r="Q17" t="s" s="27">
+        <v>54</v>
+      </c>
+      <c r="R17" t="s" s="27">
+        <v>55</v>
+      </c>
+      <c r="S17" t="s" s="26">
+        <v>44</v>
+      </c>
+      <c r="T17" t="s" s="26">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="28">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s" s="28">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s" s="28">
+        <v>47</v>
+      </c>
+      <c r="D18" t="n" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="n" s="28">
+        <v>156.0</v>
+      </c>
+      <c r="F18" t="n" s="28">
+        <v>520.0</v>
+      </c>
+      <c r="G18" t="n" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H18" t="n" s="28">
+        <v>520.0</v>
+      </c>
+      <c r="I18" t="s" s="29">
+        <v>48</v>
+      </c>
+      <c r="J18" t="s" s="28">
+        <v>49</v>
+      </c>
+      <c r="K18" t="s" s="28">
+        <v>50</v>
+      </c>
+      <c r="L18" t="s" s="28">
+        <v>51</v>
+      </c>
+      <c r="M18" t="s" s="28">
+        <v>38</v>
+      </c>
+      <c r="N18" t="s" s="28">
+        <v>39</v>
+      </c>
+      <c r="O18" t="s" s="29">
+        <v>52</v>
+      </c>
+      <c r="P18" t="s" s="29">
+        <v>53</v>
+      </c>
+      <c r="Q18" t="s" s="29">
+        <v>54</v>
+      </c>
+      <c r="R18" t="s" s="29">
+        <v>55</v>
+      </c>
+      <c r="S18" t="s" s="28">
+        <v>44</v>
+      </c>
+      <c r="T18" t="s" s="28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="30">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="D19" t="n" s="30">
+        <v>0.0</v>
+      </c>
+      <c r="E19" t="n" s="30">
+        <v>156.0</v>
+      </c>
+      <c r="F19" t="n" s="30">
+        <v>520.0</v>
+      </c>
+      <c r="G19" t="n" s="30">
+        <v>0.0</v>
+      </c>
+      <c r="H19" t="n" s="30">
+        <v>520.0</v>
+      </c>
+      <c r="I19" t="s" s="31">
+        <v>48</v>
+      </c>
+      <c r="J19" t="s" s="30">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s" s="30">
+        <v>50</v>
+      </c>
+      <c r="L19" t="s" s="30">
+        <v>51</v>
+      </c>
+      <c r="M19" t="s" s="30">
+        <v>38</v>
+      </c>
+      <c r="N19" t="s" s="30">
+        <v>39</v>
+      </c>
+      <c r="O19" t="s" s="31">
+        <v>52</v>
+      </c>
+      <c r="P19" t="s" s="31">
+        <v>53</v>
+      </c>
+      <c r="Q19" t="s" s="31">
+        <v>54</v>
+      </c>
+      <c r="R19" t="s" s="31">
+        <v>55</v>
+      </c>
+      <c r="S19" t="s" s="30">
+        <v>44</v>
+      </c>
+      <c r="T19" t="s" s="30">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="32">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s" s="32">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s" s="32">
+        <v>47</v>
+      </c>
+      <c r="D20" t="n" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E20" t="n" s="32">
+        <v>156.0</v>
+      </c>
+      <c r="F20" t="n" s="32">
+        <v>520.0</v>
+      </c>
+      <c r="G20" t="n" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="H20" t="n" s="32">
+        <v>520.0</v>
+      </c>
+      <c r="I20" t="s" s="33">
+        <v>48</v>
+      </c>
+      <c r="J20" t="s" s="32">
+        <v>49</v>
+      </c>
+      <c r="K20" t="s" s="32">
+        <v>50</v>
+      </c>
+      <c r="L20" t="s" s="32">
+        <v>51</v>
+      </c>
+      <c r="M20" t="s" s="32">
+        <v>38</v>
+      </c>
+      <c r="N20" t="s" s="32">
+        <v>39</v>
+      </c>
+      <c r="O20" t="s" s="33">
+        <v>52</v>
+      </c>
+      <c r="P20" t="s" s="33">
+        <v>53</v>
+      </c>
+      <c r="Q20" t="s" s="33">
+        <v>54</v>
+      </c>
+      <c r="R20" t="s" s="33">
+        <v>55</v>
+      </c>
+      <c r="S20" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="T20" t="s" s="32">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="34">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s" s="34">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s" s="34">
+        <v>47</v>
+      </c>
+      <c r="D21" t="n" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E21" t="n" s="34">
+        <v>156.0</v>
+      </c>
+      <c r="F21" t="n" s="34">
+        <v>520.0</v>
+      </c>
+      <c r="G21" t="n" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="H21" t="n" s="34">
+        <v>520.0</v>
+      </c>
+      <c r="I21" t="s" s="35">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s" s="34">
+        <v>49</v>
+      </c>
+      <c r="K21" t="s" s="34">
+        <v>50</v>
+      </c>
+      <c r="L21" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="M21" t="s" s="34">
+        <v>38</v>
+      </c>
+      <c r="N21" t="s" s="34">
+        <v>39</v>
+      </c>
+      <c r="O21" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="P21" t="s" s="35">
+        <v>53</v>
+      </c>
+      <c r="Q21" t="s" s="35">
+        <v>54</v>
+      </c>
+      <c r="R21" t="s" s="35">
+        <v>55</v>
+      </c>
+      <c r="S21" t="s" s="34">
+        <v>44</v>
+      </c>
+      <c r="T21" t="s" s="34">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="36">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s" s="36">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s" s="36">
+        <v>47</v>
+      </c>
+      <c r="D22" t="n" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="E22" t="n" s="36">
+        <v>156.0</v>
+      </c>
+      <c r="F22" t="n" s="36">
+        <v>520.0</v>
+      </c>
+      <c r="G22" t="n" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="H22" t="n" s="36">
+        <v>520.0</v>
+      </c>
+      <c r="I22" t="s" s="37">
+        <v>48</v>
+      </c>
+      <c r="J22" t="s" s="36">
+        <v>49</v>
+      </c>
+      <c r="K22" t="s" s="36">
+        <v>50</v>
+      </c>
+      <c r="L22" t="s" s="36">
+        <v>51</v>
+      </c>
+      <c r="M22" t="s" s="36">
+        <v>38</v>
+      </c>
+      <c r="N22" t="s" s="36">
+        <v>39</v>
+      </c>
+      <c r="O22" t="s" s="37">
+        <v>52</v>
+      </c>
+      <c r="P22" t="s" s="37">
+        <v>53</v>
+      </c>
+      <c r="Q22" t="s" s="37">
+        <v>54</v>
+      </c>
+      <c r="R22" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="S22" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="T22" t="s" s="36">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="38">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s" s="38">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s" s="38">
+        <v>47</v>
+      </c>
+      <c r="D23" t="n" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="E23" t="n" s="38">
+        <v>156.0</v>
+      </c>
+      <c r="F23" t="n" s="38">
+        <v>520.0</v>
+      </c>
+      <c r="G23" t="n" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="H23" t="n" s="38">
+        <v>520.0</v>
+      </c>
+      <c r="I23" t="s" s="39">
+        <v>48</v>
+      </c>
+      <c r="J23" t="s" s="38">
+        <v>49</v>
+      </c>
+      <c r="K23" t="s" s="38">
+        <v>50</v>
+      </c>
+      <c r="L23" t="s" s="38">
+        <v>51</v>
+      </c>
+      <c r="M23" t="s" s="38">
+        <v>38</v>
+      </c>
+      <c r="N23" t="s" s="38">
+        <v>39</v>
+      </c>
+      <c r="O23" t="s" s="39">
+        <v>52</v>
+      </c>
+      <c r="P23" t="s" s="39">
+        <v>53</v>
+      </c>
+      <c r="Q23" t="s" s="39">
+        <v>54</v>
+      </c>
+      <c r="R23" t="s" s="39">
+        <v>55</v>
+      </c>
+      <c r="S23" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="T23" t="s" s="38">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="40">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s" s="40">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s" s="40">
+        <v>47</v>
+      </c>
+      <c r="D24" t="n" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="E24" t="n" s="40">
+        <v>156.0</v>
+      </c>
+      <c r="F24" t="n" s="40">
+        <v>520.0</v>
+      </c>
+      <c r="G24" t="n" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H24" t="n" s="40">
+        <v>520.0</v>
+      </c>
+      <c r="I24" t="s" s="41">
+        <v>48</v>
+      </c>
+      <c r="J24" t="s" s="40">
+        <v>49</v>
+      </c>
+      <c r="K24" t="s" s="40">
+        <v>50</v>
+      </c>
+      <c r="L24" t="s" s="40">
+        <v>51</v>
+      </c>
+      <c r="M24" t="s" s="40">
+        <v>38</v>
+      </c>
+      <c r="N24" t="s" s="40">
+        <v>39</v>
+      </c>
+      <c r="O24" t="s" s="41">
+        <v>52</v>
+      </c>
+      <c r="P24" t="s" s="41">
+        <v>53</v>
+      </c>
+      <c r="Q24" t="s" s="41">
+        <v>54</v>
+      </c>
+      <c r="R24" t="s" s="41">
+        <v>55</v>
+      </c>
+      <c r="S24" t="s" s="40">
+        <v>44</v>
+      </c>
+      <c r="T24" t="s" s="40">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/excel/Deplacement_S2.xlsx
+++ b/excel/Deplacement_S2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="73">
   <si>
     <t>Acteur Dépense</t>
   </si>
@@ -180,6 +180,57 @@
   </si>
   <si>
     <t>78</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Ftati</t>
+  </si>
+  <si>
+    <t>Halima</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>7890876543234567</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
+    <t>EF</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>7654321123456789</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>11/09/2027</t>
   </si>
 </sst>
 </file>
@@ -252,9 +303,129 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
@@ -383,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.98046875"/>
@@ -1745,6 +1916,1246 @@
         <v>45</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s" s="42">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s" s="42">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s" s="42">
+        <v>47</v>
+      </c>
+      <c r="D25" t="n" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="E25" t="n" s="42">
+        <v>156.0</v>
+      </c>
+      <c r="F25" t="n" s="42">
+        <v>520.0</v>
+      </c>
+      <c r="G25" t="n" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H25" t="n" s="42">
+        <v>520.0</v>
+      </c>
+      <c r="I25" t="s" s="43">
+        <v>48</v>
+      </c>
+      <c r="J25" t="s" s="42">
+        <v>49</v>
+      </c>
+      <c r="K25" t="s" s="42">
+        <v>50</v>
+      </c>
+      <c r="L25" t="s" s="42">
+        <v>51</v>
+      </c>
+      <c r="M25" t="s" s="42">
+        <v>38</v>
+      </c>
+      <c r="N25" t="s" s="42">
+        <v>39</v>
+      </c>
+      <c r="O25" t="s" s="43">
+        <v>52</v>
+      </c>
+      <c r="P25" t="s" s="43">
+        <v>53</v>
+      </c>
+      <c r="Q25" t="s" s="43">
+        <v>54</v>
+      </c>
+      <c r="R25" t="s" s="43">
+        <v>55</v>
+      </c>
+      <c r="S25" t="s" s="42">
+        <v>44</v>
+      </c>
+      <c r="T25" t="s" s="42">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="44">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s" s="44">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s" s="44">
+        <v>47</v>
+      </c>
+      <c r="D26" t="n" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="n" s="44">
+        <v>156.0</v>
+      </c>
+      <c r="F26" t="n" s="44">
+        <v>520.0</v>
+      </c>
+      <c r="G26" t="n" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="H26" t="n" s="44">
+        <v>520.0</v>
+      </c>
+      <c r="I26" t="s" s="45">
+        <v>48</v>
+      </c>
+      <c r="J26" t="s" s="44">
+        <v>49</v>
+      </c>
+      <c r="K26" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="L26" t="s" s="44">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s" s="44">
+        <v>38</v>
+      </c>
+      <c r="N26" t="s" s="44">
+        <v>39</v>
+      </c>
+      <c r="O26" t="s" s="45">
+        <v>52</v>
+      </c>
+      <c r="P26" t="s" s="45">
+        <v>53</v>
+      </c>
+      <c r="Q26" t="s" s="45">
+        <v>54</v>
+      </c>
+      <c r="R26" t="s" s="45">
+        <v>55</v>
+      </c>
+      <c r="S26" t="s" s="44">
+        <v>44</v>
+      </c>
+      <c r="T26" t="s" s="44">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="46">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s" s="46">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s" s="46">
+        <v>33</v>
+      </c>
+      <c r="D27" t="n" s="46">
+        <v>0.0</v>
+      </c>
+      <c r="E27" t="n" s="46">
+        <v>156.0</v>
+      </c>
+      <c r="F27" t="n" s="46">
+        <v>1924.0</v>
+      </c>
+      <c r="G27" t="n" s="46">
+        <v>0.0</v>
+      </c>
+      <c r="H27" t="n" s="46">
+        <v>1924.0</v>
+      </c>
+      <c r="I27" t="s" s="47">
+        <v>57</v>
+      </c>
+      <c r="J27" t="s" s="46">
+        <v>58</v>
+      </c>
+      <c r="K27" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L27" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="M27" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="N27" t="s" s="46">
+        <v>39</v>
+      </c>
+      <c r="O27" t="s" s="47">
+        <v>52</v>
+      </c>
+      <c r="P27" t="s" s="47">
+        <v>53</v>
+      </c>
+      <c r="Q27" t="s" s="47">
+        <v>61</v>
+      </c>
+      <c r="R27" t="s" s="47">
+        <v>62</v>
+      </c>
+      <c r="S27" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="T27" t="s" s="46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="48">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s" s="48">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s" s="48">
+        <v>33</v>
+      </c>
+      <c r="D28" t="n" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="E28" t="n" s="48">
+        <v>156.0</v>
+      </c>
+      <c r="F28" t="n" s="48">
+        <v>1924.0</v>
+      </c>
+      <c r="G28" t="n" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="H28" t="n" s="48">
+        <v>1924.0</v>
+      </c>
+      <c r="I28" t="s" s="49">
+        <v>57</v>
+      </c>
+      <c r="J28" t="s" s="48">
+        <v>58</v>
+      </c>
+      <c r="K28" t="s" s="48">
+        <v>59</v>
+      </c>
+      <c r="L28" t="s" s="48">
+        <v>60</v>
+      </c>
+      <c r="M28" t="s" s="48">
+        <v>38</v>
+      </c>
+      <c r="N28" t="s" s="48">
+        <v>39</v>
+      </c>
+      <c r="O28" t="s" s="49">
+        <v>52</v>
+      </c>
+      <c r="P28" t="s" s="49">
+        <v>53</v>
+      </c>
+      <c r="Q28" t="s" s="49">
+        <v>61</v>
+      </c>
+      <c r="R28" t="s" s="49">
+        <v>62</v>
+      </c>
+      <c r="S28" t="s" s="48">
+        <v>44</v>
+      </c>
+      <c r="T28" t="s" s="48">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="50">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s" s="50">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s" s="50">
+        <v>33</v>
+      </c>
+      <c r="D29" t="n" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="E29" t="n" s="50">
+        <v>156.0</v>
+      </c>
+      <c r="F29" t="n" s="50">
+        <v>1924.0</v>
+      </c>
+      <c r="G29" t="n" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="H29" t="n" s="50">
+        <v>1924.0</v>
+      </c>
+      <c r="I29" t="s" s="51">
+        <v>57</v>
+      </c>
+      <c r="J29" t="s" s="50">
+        <v>58</v>
+      </c>
+      <c r="K29" t="s" s="50">
+        <v>59</v>
+      </c>
+      <c r="L29" t="s" s="50">
+        <v>60</v>
+      </c>
+      <c r="M29" t="s" s="50">
+        <v>38</v>
+      </c>
+      <c r="N29" t="s" s="50">
+        <v>39</v>
+      </c>
+      <c r="O29" t="s" s="51">
+        <v>52</v>
+      </c>
+      <c r="P29" t="s" s="51">
+        <v>53</v>
+      </c>
+      <c r="Q29" t="s" s="51">
+        <v>61</v>
+      </c>
+      <c r="R29" t="s" s="51">
+        <v>62</v>
+      </c>
+      <c r="S29" t="s" s="50">
+        <v>44</v>
+      </c>
+      <c r="T29" t="s" s="50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="52">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s" s="52">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s" s="52">
+        <v>33</v>
+      </c>
+      <c r="D30" t="n" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="E30" t="n" s="52">
+        <v>156.0</v>
+      </c>
+      <c r="F30" t="n" s="52">
+        <v>1924.0</v>
+      </c>
+      <c r="G30" t="n" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="H30" t="n" s="52">
+        <v>1924.0</v>
+      </c>
+      <c r="I30" t="s" s="53">
+        <v>57</v>
+      </c>
+      <c r="J30" t="s" s="52">
+        <v>58</v>
+      </c>
+      <c r="K30" t="s" s="52">
+        <v>59</v>
+      </c>
+      <c r="L30" t="s" s="52">
+        <v>60</v>
+      </c>
+      <c r="M30" t="s" s="52">
+        <v>38</v>
+      </c>
+      <c r="N30" t="s" s="52">
+        <v>39</v>
+      </c>
+      <c r="O30" t="s" s="53">
+        <v>52</v>
+      </c>
+      <c r="P30" t="s" s="53">
+        <v>53</v>
+      </c>
+      <c r="Q30" t="s" s="53">
+        <v>61</v>
+      </c>
+      <c r="R30" t="s" s="53">
+        <v>62</v>
+      </c>
+      <c r="S30" t="s" s="52">
+        <v>44</v>
+      </c>
+      <c r="T30" t="s" s="52">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="54">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s" s="54">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s" s="54">
+        <v>33</v>
+      </c>
+      <c r="D31" t="n" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="E31" t="n" s="54">
+        <v>156.0</v>
+      </c>
+      <c r="F31" t="n" s="54">
+        <v>1924.0</v>
+      </c>
+      <c r="G31" t="n" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="H31" t="n" s="54">
+        <v>1924.0</v>
+      </c>
+      <c r="I31" t="s" s="55">
+        <v>57</v>
+      </c>
+      <c r="J31" t="s" s="54">
+        <v>58</v>
+      </c>
+      <c r="K31" t="s" s="54">
+        <v>59</v>
+      </c>
+      <c r="L31" t="s" s="54">
+        <v>60</v>
+      </c>
+      <c r="M31" t="s" s="54">
+        <v>38</v>
+      </c>
+      <c r="N31" t="s" s="54">
+        <v>39</v>
+      </c>
+      <c r="O31" t="s" s="55">
+        <v>52</v>
+      </c>
+      <c r="P31" t="s" s="55">
+        <v>53</v>
+      </c>
+      <c r="Q31" t="s" s="55">
+        <v>61</v>
+      </c>
+      <c r="R31" t="s" s="55">
+        <v>62</v>
+      </c>
+      <c r="S31" t="s" s="54">
+        <v>44</v>
+      </c>
+      <c r="T31" t="s" s="54">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="56">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s" s="56">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s" s="56">
+        <v>33</v>
+      </c>
+      <c r="D32" t="n" s="56">
+        <v>0.0</v>
+      </c>
+      <c r="E32" t="n" s="56">
+        <v>156.0</v>
+      </c>
+      <c r="F32" t="n" s="56">
+        <v>300.0</v>
+      </c>
+      <c r="G32" t="n" s="56">
+        <v>0.0</v>
+      </c>
+      <c r="H32" t="n" s="56">
+        <v>300.0</v>
+      </c>
+      <c r="I32" t="s" s="57">
+        <v>57</v>
+      </c>
+      <c r="J32" t="s" s="56">
+        <v>58</v>
+      </c>
+      <c r="K32" t="s" s="56">
+        <v>59</v>
+      </c>
+      <c r="L32" t="s" s="56">
+        <v>60</v>
+      </c>
+      <c r="M32" t="s" s="56">
+        <v>38</v>
+      </c>
+      <c r="N32" t="s" s="56">
+        <v>39</v>
+      </c>
+      <c r="O32" t="s" s="57">
+        <v>52</v>
+      </c>
+      <c r="P32" t="s" s="57">
+        <v>53</v>
+      </c>
+      <c r="Q32" t="s" s="57">
+        <v>61</v>
+      </c>
+      <c r="R32" t="s" s="57">
+        <v>62</v>
+      </c>
+      <c r="S32" t="s" s="56">
+        <v>44</v>
+      </c>
+      <c r="T32" t="s" s="56">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="58">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="58">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s" s="58">
+        <v>33</v>
+      </c>
+      <c r="D33" t="n" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="E33" t="n" s="58">
+        <v>156.0</v>
+      </c>
+      <c r="F33" t="n" s="58">
+        <v>300.0</v>
+      </c>
+      <c r="G33" t="n" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="H33" t="n" s="58">
+        <v>300.0</v>
+      </c>
+      <c r="I33" t="s" s="59">
+        <v>57</v>
+      </c>
+      <c r="J33" t="s" s="58">
+        <v>58</v>
+      </c>
+      <c r="K33" t="s" s="58">
+        <v>59</v>
+      </c>
+      <c r="L33" t="s" s="58">
+        <v>60</v>
+      </c>
+      <c r="M33" t="s" s="58">
+        <v>38</v>
+      </c>
+      <c r="N33" t="s" s="58">
+        <v>39</v>
+      </c>
+      <c r="O33" t="s" s="59">
+        <v>52</v>
+      </c>
+      <c r="P33" t="s" s="59">
+        <v>53</v>
+      </c>
+      <c r="Q33" t="s" s="59">
+        <v>61</v>
+      </c>
+      <c r="R33" t="s" s="59">
+        <v>62</v>
+      </c>
+      <c r="S33" t="s" s="58">
+        <v>44</v>
+      </c>
+      <c r="T33" t="s" s="58">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="60">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s" s="60">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s" s="60">
+        <v>33</v>
+      </c>
+      <c r="D34" t="n" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="E34" t="n" s="60">
+        <v>156.0</v>
+      </c>
+      <c r="F34" t="n" s="60">
+        <v>300.0</v>
+      </c>
+      <c r="G34" t="n" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="H34" t="n" s="60">
+        <v>300.0</v>
+      </c>
+      <c r="I34" t="s" s="61">
+        <v>57</v>
+      </c>
+      <c r="J34" t="s" s="60">
+        <v>58</v>
+      </c>
+      <c r="K34" t="s" s="60">
+        <v>59</v>
+      </c>
+      <c r="L34" t="s" s="60">
+        <v>60</v>
+      </c>
+      <c r="M34" t="s" s="60">
+        <v>38</v>
+      </c>
+      <c r="N34" t="s" s="60">
+        <v>39</v>
+      </c>
+      <c r="O34" t="s" s="61">
+        <v>52</v>
+      </c>
+      <c r="P34" t="s" s="61">
+        <v>53</v>
+      </c>
+      <c r="Q34" t="s" s="61">
+        <v>61</v>
+      </c>
+      <c r="R34" t="s" s="61">
+        <v>62</v>
+      </c>
+      <c r="S34" t="s" s="60">
+        <v>44</v>
+      </c>
+      <c r="T34" t="s" s="60">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="62">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s" s="62">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s" s="62">
+        <v>33</v>
+      </c>
+      <c r="D35" t="n" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="E35" t="n" s="62">
+        <v>156.0</v>
+      </c>
+      <c r="F35" t="n" s="62">
+        <v>300.0</v>
+      </c>
+      <c r="G35" t="n" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="H35" t="n" s="62">
+        <v>300.0</v>
+      </c>
+      <c r="I35" t="s" s="63">
+        <v>57</v>
+      </c>
+      <c r="J35" t="s" s="62">
+        <v>58</v>
+      </c>
+      <c r="K35" t="s" s="62">
+        <v>59</v>
+      </c>
+      <c r="L35" t="s" s="62">
+        <v>60</v>
+      </c>
+      <c r="M35" t="s" s="62">
+        <v>38</v>
+      </c>
+      <c r="N35" t="s" s="62">
+        <v>39</v>
+      </c>
+      <c r="O35" t="s" s="63">
+        <v>52</v>
+      </c>
+      <c r="P35" t="s" s="63">
+        <v>53</v>
+      </c>
+      <c r="Q35" t="s" s="63">
+        <v>61</v>
+      </c>
+      <c r="R35" t="s" s="63">
+        <v>62</v>
+      </c>
+      <c r="S35" t="s" s="62">
+        <v>44</v>
+      </c>
+      <c r="T35" t="s" s="62">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="64">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s" s="64">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s" s="64">
+        <v>33</v>
+      </c>
+      <c r="D36" t="n" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="E36" t="n" s="64">
+        <v>156.0</v>
+      </c>
+      <c r="F36" t="n" s="64">
+        <v>300.0</v>
+      </c>
+      <c r="G36" t="n" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="H36" t="n" s="64">
+        <v>300.0</v>
+      </c>
+      <c r="I36" t="s" s="65">
+        <v>57</v>
+      </c>
+      <c r="J36" t="s" s="64">
+        <v>58</v>
+      </c>
+      <c r="K36" t="s" s="64">
+        <v>59</v>
+      </c>
+      <c r="L36" t="s" s="64">
+        <v>60</v>
+      </c>
+      <c r="M36" t="s" s="64">
+        <v>38</v>
+      </c>
+      <c r="N36" t="s" s="64">
+        <v>39</v>
+      </c>
+      <c r="O36" t="s" s="65">
+        <v>52</v>
+      </c>
+      <c r="P36" t="s" s="65">
+        <v>53</v>
+      </c>
+      <c r="Q36" t="s" s="65">
+        <v>61</v>
+      </c>
+      <c r="R36" t="s" s="65">
+        <v>62</v>
+      </c>
+      <c r="S36" t="s" s="64">
+        <v>44</v>
+      </c>
+      <c r="T36" t="s" s="64">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="66">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s" s="66">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s" s="66">
+        <v>33</v>
+      </c>
+      <c r="D37" t="n" s="66">
+        <v>0.0</v>
+      </c>
+      <c r="E37" t="n" s="66">
+        <v>156.0</v>
+      </c>
+      <c r="F37" t="n" s="66">
+        <v>300.0</v>
+      </c>
+      <c r="G37" t="n" s="66">
+        <v>0.0</v>
+      </c>
+      <c r="H37" t="n" s="66">
+        <v>300.0</v>
+      </c>
+      <c r="I37" t="s" s="67">
+        <v>57</v>
+      </c>
+      <c r="J37" t="s" s="66">
+        <v>58</v>
+      </c>
+      <c r="K37" t="s" s="66">
+        <v>59</v>
+      </c>
+      <c r="L37" t="s" s="66">
+        <v>60</v>
+      </c>
+      <c r="M37" t="s" s="66">
+        <v>38</v>
+      </c>
+      <c r="N37" t="s" s="66">
+        <v>39</v>
+      </c>
+      <c r="O37" t="s" s="67">
+        <v>52</v>
+      </c>
+      <c r="P37" t="s" s="67">
+        <v>53</v>
+      </c>
+      <c r="Q37" t="s" s="67">
+        <v>61</v>
+      </c>
+      <c r="R37" t="s" s="67">
+        <v>62</v>
+      </c>
+      <c r="S37" t="s" s="66">
+        <v>44</v>
+      </c>
+      <c r="T37" t="s" s="66">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="68">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s" s="68">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s" s="68">
+        <v>33</v>
+      </c>
+      <c r="D38" t="n" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="E38" t="n" s="68">
+        <v>156.0</v>
+      </c>
+      <c r="F38" t="n" s="68">
+        <v>300.0</v>
+      </c>
+      <c r="G38" t="n" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="H38" t="n" s="68">
+        <v>300.0</v>
+      </c>
+      <c r="I38" t="s" s="69">
+        <v>57</v>
+      </c>
+      <c r="J38" t="s" s="68">
+        <v>58</v>
+      </c>
+      <c r="K38" t="s" s="68">
+        <v>59</v>
+      </c>
+      <c r="L38" t="s" s="68">
+        <v>60</v>
+      </c>
+      <c r="M38" t="s" s="68">
+        <v>38</v>
+      </c>
+      <c r="N38" t="s" s="68">
+        <v>39</v>
+      </c>
+      <c r="O38" t="s" s="69">
+        <v>52</v>
+      </c>
+      <c r="P38" t="s" s="69">
+        <v>53</v>
+      </c>
+      <c r="Q38" t="s" s="69">
+        <v>61</v>
+      </c>
+      <c r="R38" t="s" s="69">
+        <v>62</v>
+      </c>
+      <c r="S38" t="s" s="68">
+        <v>44</v>
+      </c>
+      <c r="T38" t="s" s="68">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="70">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s" s="70">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s" s="70">
+        <v>33</v>
+      </c>
+      <c r="D39" t="n" s="70">
+        <v>0.0</v>
+      </c>
+      <c r="E39" t="n" s="70">
+        <v>156.0</v>
+      </c>
+      <c r="F39" t="n" s="70">
+        <v>300.0</v>
+      </c>
+      <c r="G39" t="n" s="70">
+        <v>0.0</v>
+      </c>
+      <c r="H39" t="n" s="70">
+        <v>300.0</v>
+      </c>
+      <c r="I39" t="s" s="71">
+        <v>57</v>
+      </c>
+      <c r="J39" t="s" s="70">
+        <v>58</v>
+      </c>
+      <c r="K39" t="s" s="70">
+        <v>59</v>
+      </c>
+      <c r="L39" t="s" s="70">
+        <v>60</v>
+      </c>
+      <c r="M39" t="s" s="70">
+        <v>38</v>
+      </c>
+      <c r="N39" t="s" s="70">
+        <v>39</v>
+      </c>
+      <c r="O39" t="s" s="71">
+        <v>52</v>
+      </c>
+      <c r="P39" t="s" s="71">
+        <v>53</v>
+      </c>
+      <c r="Q39" t="s" s="71">
+        <v>61</v>
+      </c>
+      <c r="R39" t="s" s="71">
+        <v>62</v>
+      </c>
+      <c r="S39" t="s" s="70">
+        <v>44</v>
+      </c>
+      <c r="T39" t="s" s="70">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="72">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s" s="72">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s" s="72">
+        <v>33</v>
+      </c>
+      <c r="D40" t="n" s="72">
+        <v>0.0</v>
+      </c>
+      <c r="E40" t="n" s="72">
+        <v>156.0</v>
+      </c>
+      <c r="F40" t="n" s="72">
+        <v>300.0</v>
+      </c>
+      <c r="G40" t="n" s="72">
+        <v>0.0</v>
+      </c>
+      <c r="H40" t="n" s="72">
+        <v>300.0</v>
+      </c>
+      <c r="I40" t="s" s="73">
+        <v>57</v>
+      </c>
+      <c r="J40" t="s" s="72">
+        <v>58</v>
+      </c>
+      <c r="K40" t="s" s="72">
+        <v>59</v>
+      </c>
+      <c r="L40" t="s" s="72">
+        <v>60</v>
+      </c>
+      <c r="M40" t="s" s="72">
+        <v>38</v>
+      </c>
+      <c r="N40" t="s" s="72">
+        <v>39</v>
+      </c>
+      <c r="O40" t="s" s="73">
+        <v>52</v>
+      </c>
+      <c r="P40" t="s" s="73">
+        <v>53</v>
+      </c>
+      <c r="Q40" t="s" s="73">
+        <v>61</v>
+      </c>
+      <c r="R40" t="s" s="73">
+        <v>62</v>
+      </c>
+      <c r="S40" t="s" s="72">
+        <v>44</v>
+      </c>
+      <c r="T40" t="s" s="72">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="74">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s" s="74">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s" s="74">
+        <v>33</v>
+      </c>
+      <c r="D41" t="n" s="74">
+        <v>0.0</v>
+      </c>
+      <c r="E41" t="n" s="74">
+        <v>156.0</v>
+      </c>
+      <c r="F41" t="n" s="74">
+        <v>300.0</v>
+      </c>
+      <c r="G41" t="n" s="74">
+        <v>0.0</v>
+      </c>
+      <c r="H41" t="n" s="74">
+        <v>300.0</v>
+      </c>
+      <c r="I41" t="s" s="75">
+        <v>57</v>
+      </c>
+      <c r="J41" t="s" s="74">
+        <v>58</v>
+      </c>
+      <c r="K41" t="s" s="74">
+        <v>59</v>
+      </c>
+      <c r="L41" t="s" s="74">
+        <v>60</v>
+      </c>
+      <c r="M41" t="s" s="74">
+        <v>38</v>
+      </c>
+      <c r="N41" t="s" s="74">
+        <v>39</v>
+      </c>
+      <c r="O41" t="s" s="75">
+        <v>52</v>
+      </c>
+      <c r="P41" t="s" s="75">
+        <v>53</v>
+      </c>
+      <c r="Q41" t="s" s="75">
+        <v>61</v>
+      </c>
+      <c r="R41" t="s" s="75">
+        <v>62</v>
+      </c>
+      <c r="S41" t="s" s="74">
+        <v>44</v>
+      </c>
+      <c r="T41" t="s" s="74">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="76">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s" s="76">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s" s="76">
+        <v>33</v>
+      </c>
+      <c r="D42" t="n" s="76">
+        <v>0.0</v>
+      </c>
+      <c r="E42" t="n" s="76">
+        <v>156.0</v>
+      </c>
+      <c r="F42" t="n" s="76">
+        <v>300.0</v>
+      </c>
+      <c r="G42" t="n" s="76">
+        <v>0.0</v>
+      </c>
+      <c r="H42" t="n" s="76">
+        <v>300.0</v>
+      </c>
+      <c r="I42" t="s" s="77">
+        <v>57</v>
+      </c>
+      <c r="J42" t="s" s="76">
+        <v>58</v>
+      </c>
+      <c r="K42" t="s" s="76">
+        <v>59</v>
+      </c>
+      <c r="L42" t="s" s="76">
+        <v>60</v>
+      </c>
+      <c r="M42" t="s" s="76">
+        <v>38</v>
+      </c>
+      <c r="N42" t="s" s="76">
+        <v>39</v>
+      </c>
+      <c r="O42" t="s" s="77">
+        <v>52</v>
+      </c>
+      <c r="P42" t="s" s="77">
+        <v>53</v>
+      </c>
+      <c r="Q42" t="s" s="77">
+        <v>61</v>
+      </c>
+      <c r="R42" t="s" s="77">
+        <v>62</v>
+      </c>
+      <c r="S42" t="s" s="76">
+        <v>44</v>
+      </c>
+      <c r="T42" t="s" s="76">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="78">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s" s="78">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s" s="78">
+        <v>64</v>
+      </c>
+      <c r="D43" t="n" s="78">
+        <v>18.0</v>
+      </c>
+      <c r="E43" t="n" s="78">
+        <v>0.0</v>
+      </c>
+      <c r="F43" t="n" s="78">
+        <v>360.0</v>
+      </c>
+      <c r="G43" t="n" s="78">
+        <v>0.0</v>
+      </c>
+      <c r="H43" t="n" s="78">
+        <v>360.0</v>
+      </c>
+      <c r="I43" t="s" s="79">
+        <v>65</v>
+      </c>
+      <c r="J43" t="s" s="78">
+        <v>66</v>
+      </c>
+      <c r="K43" t="s" s="78">
+        <v>67</v>
+      </c>
+      <c r="L43" t="s" s="78">
+        <v>60</v>
+      </c>
+      <c r="M43" t="s" s="78">
+        <v>38</v>
+      </c>
+      <c r="N43" t="s" s="78">
+        <v>39</v>
+      </c>
+      <c r="O43" t="s" s="79">
+        <v>68</v>
+      </c>
+      <c r="P43" t="s" s="79">
+        <v>69</v>
+      </c>
+      <c r="Q43" t="s" s="79">
+        <v>70</v>
+      </c>
+      <c r="R43" t="s" s="79">
+        <v>71</v>
+      </c>
+      <c r="S43" t="s" s="78">
+        <v>44</v>
+      </c>
+      <c r="T43" t="s" s="78">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="80">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s" s="80">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s" s="80">
+        <v>72</v>
+      </c>
+      <c r="D44" t="n" s="80">
+        <v>28.0</v>
+      </c>
+      <c r="E44" t="n" s="80">
+        <v>20.0</v>
+      </c>
+      <c r="F44" t="n" s="80">
+        <v>560.0</v>
+      </c>
+      <c r="G44" t="n" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="H44" t="n" s="80">
+        <v>560.0</v>
+      </c>
+      <c r="I44" t="s" s="81">
+        <v>65</v>
+      </c>
+      <c r="J44" t="s" s="80">
+        <v>66</v>
+      </c>
+      <c r="K44" t="s" s="80">
+        <v>67</v>
+      </c>
+      <c r="L44" t="s" s="80">
+        <v>60</v>
+      </c>
+      <c r="M44" t="s" s="80">
+        <v>38</v>
+      </c>
+      <c r="N44" t="s" s="80">
+        <v>39</v>
+      </c>
+      <c r="O44" t="s" s="81">
+        <v>68</v>
+      </c>
+      <c r="P44" t="s" s="81">
+        <v>69</v>
+      </c>
+      <c r="Q44" t="s" s="81">
+        <v>70</v>
+      </c>
+      <c r="R44" t="s" s="81">
+        <v>71</v>
+      </c>
+      <c r="S44" t="s" s="80">
+        <v>44</v>
+      </c>
+      <c r="T44" t="s" s="80">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
